--- a/output/2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zona PIP / Via Einstein Lotto 24, Lavello (PZ). Il marchio e-commerce 'Signore Shop' (signoreshop.com) risulta associato a questa sede e a questo telefono.</t>
+          <t>Zona PIP / Via Einstein Lotto 24, Lavello (PZ). Il marchio e-commerce 'Signore Shop' (signoreshop.com) risulta associato a questa sede e a questo telefono. [DUPLICATO — vedi anche: 2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
